--- a/objects/vax_analysis.xlsx
+++ b/objects/vax_analysis.xlsx
@@ -9,33 +9,26 @@
     <sheet name="vax_statusAfter one dose" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="vax_statusAfter two doses" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="vax_statusAfter booster" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AnyCancerPhe1" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="SexF" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="RaceEthnicity4African Americ..." sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="RaceEthnicity4Other_Unknown" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t xml:space="preserve">model</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t xml:space="preserve">term</t>
   </si>
   <si>
-    <t xml:space="preserve">Severe COVID</t>
+    <t xml:space="preserve">severe_covid</t>
   </si>
   <si>
-    <t xml:space="preserve">Hospitalized</t>
+    <t xml:space="preserve">hospitalized</t>
   </si>
   <si>
-    <t xml:space="preserve">ICU</t>
+    <t xml:space="preserve">icu</t>
   </si>
   <si>
-    <t xml:space="preserve">Deceased</t>
+    <t xml:space="preserve">death</t>
   </si>
 </sst>
 </file>
@@ -380,9 +373,6 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -411,9 +401,6 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -442,133 +429,6 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/objects/vax_analysis.xlsx
+++ b/objects/vax_analysis.xlsx
@@ -6,15 +6,15 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="vax_statusAfter one dose" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="vax_statusAfter two doses" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="vax_statusAfter booster" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="factor(vax_status)After one ..." sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="factor(vax_status)After two ..." sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="factor(vax_status)After booster" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t xml:space="preserve">term</t>
   </si>
@@ -29,6 +29,21 @@
   </si>
   <si>
     <t xml:space="preserve">death</t>
+  </si>
+  <si>
+    <t xml:space="preserve">factor(vax_status)After booster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31 (0.21, 0.43)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35 (0.24, 0.49)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29 (0.12, 0.59)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09 (0.01, 0.32)</t>
   </si>
 </sst>
 </file>
@@ -430,6 +445,23 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/objects/vax_analysis.xlsx
+++ b/objects/vax_analysis.xlsx
@@ -6,15 +6,15 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="vax_statusAfter one dose" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="vax_statusAfter two doses" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="vax_statusAfter booster" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="After one dose" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="After two doses" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="After booster" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t xml:space="preserve">term</t>
   </si>
@@ -29,6 +29,51 @@
   </si>
   <si>
     <t xml:space="preserve">death</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After one dose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.57 (0.39, 0.81)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63 (0.43, 0.89)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37 (0.12, 0.84)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17 (0.02, 0.62)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After two doses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.48 (0.34, 0.65)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54 (0.38, 0.74)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14 (0.03, 0.40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04 (0.00, 0.26)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After booster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31 (0.21, 0.43)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35 (0.24, 0.49)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.29 (0.12, 0.59)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09 (0.01, 0.32)</t>
   </si>
 </sst>
 </file>
@@ -374,6 +419,23 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -402,6 +464,23 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -430,6 +509,23 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
